--- a/reference_data/testes_excluidos.xlsx
+++ b/reference_data/testes_excluidos.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligiagracindo\OneDrive - LABORATORIO SABIN DE ANALISES CLINICAS LTDA\Área de Trabalho\Modulo CIQ\modulo_CIQ_PBI\exportar_powerbi\reference_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8AEFC0-2FAF-4A31-ABE5-A89577E1F383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t>Teste</t>
   </si>
@@ -29,13 +48,82 @@
   </si>
   <si>
     <t>Teste reflexo</t>
+  </si>
+  <si>
+    <t>PSALIQ</t>
+  </si>
+  <si>
+    <t>CMVA IGG</t>
+  </si>
+  <si>
+    <t>TOXAREFL</t>
+  </si>
+  <si>
+    <t>TOXAAVIL</t>
+  </si>
+  <si>
+    <t>AMI12</t>
+  </si>
+  <si>
+    <t>AMILASD2</t>
+  </si>
+  <si>
+    <t>AURU24H</t>
+  </si>
+  <si>
+    <t>CAUI</t>
+  </si>
+  <si>
+    <t>CL_LIQ</t>
+  </si>
+  <si>
+    <t>CLORODIV</t>
+  </si>
+  <si>
+    <t>CLOUI</t>
+  </si>
+  <si>
+    <t>CMVA AVI</t>
+  </si>
+  <si>
+    <t>AMI24</t>
+  </si>
+  <si>
+    <t>CREUI</t>
+  </si>
+  <si>
+    <t>KUI</t>
+  </si>
+  <si>
+    <t>LACTLCR</t>
+  </si>
+  <si>
+    <t>MAGUI</t>
+  </si>
+  <si>
+    <t>MICRO12</t>
+  </si>
+  <si>
+    <t>MICROI</t>
+  </si>
+  <si>
+    <t>NAUI</t>
+  </si>
+  <si>
+    <t>PTPLEURA</t>
+  </si>
+  <si>
+    <t>TOXOA L</t>
+  </si>
+  <si>
+    <t>URUI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,13 +160,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -116,7 +212,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -150,6 +246,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -184,9 +281,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -359,11 +457,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -371,7 +469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -379,15 +477,487 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100568F5CC05C0EB141976077D955B69C35" ma:contentTypeVersion="16" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="d4ca6529424555f374aad7cb012476eb">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="f4f09fc9-7c38-48f6-a081-4c097487ccb2" xmlns:ns3="473fc20c-a8e5-4539-a187-fca033d19e7f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97dfbb2c9e816302c7fa669abc1f33f7" ns1:_="" ns2:_="" ns3:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="f4f09fc9-7c38-48f6-a081-4c097487ccb2"/>
+    <xsd:import namespace="473fc20c-a8e5-4539-a187-fca033d19e7f"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="22" nillable="true" ma:displayName="Propriedades da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="23" nillable="true" ma:displayName="Ação de Interface do Usuário da Política de Conformidade Unificada" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4f09fc9-7c38-48f6-a081-4c097487ccb2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="32531592-a77b-4a4b-95d3-a4c0b044061b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="473fc20c-a8e5-4539-a187-fca033d19e7f" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{59c8a8fd-ba0b-43e5-8a4a-b68fbf995f2a}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="473fc20c-a8e5-4539-a187-fca033d19e7f">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="473fc20c-a8e5-4539-a187-fca033d19e7f" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4f09fc9-7c38-48f6-a081-4c097487ccb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0266FC8-8C4D-4A96-AAAB-50DFA8BC9721}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81F76298-014A-4D05-9176-D43C19292DFC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F31FF9FD-7DAD-47A8-ABBC-593BC462CA4D}"/>
 </file>